--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:30</t>
+          <t>2026-10-14 14:14:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1727,7 +1727,11 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>( &lt;http://publications.europa.eu/resource/authority/access-right/PUBLIC&gt; &lt;http://publications.europa.eu/resource/authority/access-right/RESTRICTED&gt; &lt;http://publications.europa.eu/resource/authority/access-right/NON_PUBLIC&gt; )</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1739,7 +1743,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dash:URIEditor</t>
+          <t>dash:EnumSelectEditor</t>
         </is>
       </c>
     </row>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-DatasetShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-DatasetShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:48</t>
+          <t>2026-10-14 14:30:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#DatasetShape</t>
+          <t>http://data.health-ri.nl/core/p2/DatasetShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:accessRights</t>
+          <t>hrishapes:DatasetShape#dct:accessRights</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1750,12 +1767,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:alternative</t>
+          <t>hrishapes:DatasetShape#dct:alternative</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1808,12 +1825,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:analytics</t>
+          <t>hrishapes:DatasetShape#healthdcatap:analytics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1866,12 +1883,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/hri:anatomicalLocationCovered</t>
+          <t>hrishapes:DatasetShape#hri:anatomicalLocationCovered</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1928,12 +1945,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcatap:applicableLegislation</t>
+          <t>hrishapes:DatasetShape#dcatap:applicableLegislation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1992,12 +2009,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:hasCodeValues</t>
+          <t>hrishapes:DatasetShape#healthdcatap:hasCodeValues</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2050,12 +2067,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:hasCodingSystem</t>
+          <t>hrishapes:DatasetShape#healthdcatap:hasCodingSystem</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2108,12 +2125,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:conformsTo</t>
+          <t>hrishapes:DatasetShape#dct:conformsTo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2166,12 +2183,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:contactPoint</t>
+          <t>hrishapes:DatasetShape#dcat:contactPoint</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2228,12 +2245,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:creator</t>
+          <t>hrishapes:DatasetShape#dct:creator</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2288,12 +2305,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:description</t>
+          <t>hrishapes:DatasetShape#dct:description</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2350,12 +2367,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:distribution</t>
+          <t>hrishapes:DatasetShape#dcat:distribution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2408,12 +2425,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/foaf:page</t>
+          <t>hrishapes:DatasetShape#foaf:page</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2466,12 +2483,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/edam:has_topic</t>
+          <t>hrishapes:DatasetShape#edam:has_topic</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2524,12 +2541,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:accrualPeriodicity</t>
+          <t>hrishapes:DatasetShape#dct:accrualPeriodicity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2584,12 +2601,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:spatial</t>
+          <t>hrishapes:DatasetShape#dct:spatial</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2642,12 +2659,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:hasVersion</t>
+          <t>hrishapes:DatasetShape#dcat:hasVersion</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2700,12 +2717,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/hri:healthConditionOfInterest</t>
+          <t>hrishapes:DatasetShape#hri:healthConditionOfInterest</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2762,12 +2779,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:healthTheme</t>
+          <t>hrishapes:DatasetShape#healthdcatap:healthTheme</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2820,12 +2837,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:identifier</t>
+          <t>hrishapes:DatasetShape#dct:identifier</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2882,12 +2899,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:inSeries</t>
+          <t>hrishapes:DatasetShape#dcat:inSeries</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2940,12 +2957,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:isReferencedBy</t>
+          <t>hrishapes:DatasetShape#dct:isReferencedBy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2998,12 +3015,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:keyword</t>
+          <t>hrishapes:DatasetShape#dcat:keyword</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3058,12 +3075,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:landingPage</t>
+          <t>hrishapes:DatasetShape#dcat:landingPage</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3116,12 +3133,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:language</t>
+          <t>hrishapes:DatasetShape#dct:language</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3174,12 +3191,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dpv:hasLegalBasis</t>
+          <t>hrishapes:DatasetShape#dpv:hasLegalBasis</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3232,12 +3249,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:maxTypicalAge</t>
+          <t>hrishapes:DatasetShape#healthdcatap:maxTypicalAge</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3296,12 +3313,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:minTypicalAge</t>
+          <t>hrishapes:DatasetShape#healthdcatap:minTypicalAge</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3360,12 +3377,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/schema:measurementTechnique</t>
+          <t>hrishapes:DatasetShape#schema:measurementTechnique</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3418,12 +3435,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:modified</t>
+          <t>hrishapes:DatasetShape#dct:modified</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3486,12 +3503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:numberOfRecords</t>
+          <t>hrishapes:DatasetShape#healthdcatap:numberOfRecords</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3550,12 +3567,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:numberOfUniqueIndividuals</t>
+          <t>hrishapes:DatasetShape#healthdcatap:numberOfUniqueIndividuals</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3614,12 +3631,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/adms:identifier</t>
+          <t>hrishapes:DatasetShape#adms:identifier</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3672,12 +3689,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dpv:hasPersonalData</t>
+          <t>hrishapes:DatasetShape#dpv:hasPersonalData</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3730,12 +3747,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:populationCoverage</t>
+          <t>hrishapes:DatasetShape#healthdcatap:populationCoverage</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3788,12 +3805,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:provenance</t>
+          <t>hrishapes:DatasetShape#dct:provenance</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3842,12 +3859,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:publisher</t>
+          <t>hrishapes:DatasetShape#dct:publisher</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3904,12 +3921,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dpv:hasPurpose</t>
+          <t>hrishapes:DatasetShape#dpv:hasPurpose</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3962,12 +3979,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/prov:qualifiedAttribution</t>
+          <t>hrishapes:DatasetShape#prov:qualifiedAttribution</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4020,12 +4037,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:qualifiedRelation</t>
+          <t>hrishapes:DatasetShape#dcat:qualifiedRelation</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4078,12 +4095,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dqv:hasQualityAnnotation</t>
+          <t>hrishapes:DatasetShape#dqv:hasQualityAnnotation</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4136,12 +4153,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:issued</t>
+          <t>hrishapes:DatasetShape#dct:issued</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4204,12 +4221,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:retentionPeriod</t>
+          <t>hrishapes:DatasetShape#healthdcatap:retentionPeriod</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4264,12 +4281,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/adms:sample</t>
+          <t>hrishapes:DatasetShape#adms:sample</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4322,12 +4339,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:source</t>
+          <t>hrishapes:DatasetShape#dct:source</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4380,12 +4397,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/adms:status</t>
+          <t>hrishapes:DatasetShape#adms:status</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4440,12 +4457,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:temporal</t>
+          <t>hrishapes:DatasetShape#dct:temporal</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4498,12 +4515,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:temporalResolution</t>
+          <t>hrishapes:DatasetShape#dcat:temporalResolution</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4562,12 +4579,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:theme</t>
+          <t>hrishapes:DatasetShape#dcat:theme</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4626,12 +4643,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:title</t>
+          <t>hrishapes:DatasetShape#dct:title</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4688,12 +4705,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dct:type</t>
+          <t>hrishapes:DatasetShape#dct:type</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4746,12 +4763,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/healthdcatap:hasVariables</t>
+          <t>hrishapes:DatasetShape#healthdcatap:hasVariables</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4804,12 +4821,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/dcat:version</t>
+          <t>hrishapes:DatasetShape#dcat:version</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4864,12 +4881,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/adms:versionNotes</t>
+          <t>hrishapes:DatasetShape#adms:versionNotes</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4924,12 +4941,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>hri:DatasetShape/prov:wasGeneratedBy</t>
+          <t>hrishapes:DatasetShape#prov:wasGeneratedBy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hri:DatasetShape</t>
+          <t>hrishapes:DatasetShape</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:37</t>
+          <t>2026-10-19 15:50:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1922,7 +1922,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>^http://snomed\\.info/id/[0-9]{6,18}$</t>
+          <t>^http://snomed\.info/id/[0-9]{6,18}$</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1933,7 +1933,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2055,7 +2055,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#KindShape</t>
+          <t>http://data.health-ri.nl/core/p2/KindShape</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AgentShape</t>
+          <t>http://data.health-ri.nl/core/p2/AgentShape</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2589,7 +2589,7 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2647,7 +2647,7 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -2756,7 +2756,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>^(http://snomed\\.info/id/[0-9]{6,18}|http://id\\.who\\.int/icd/entity/[0-9]+|http://www\\.orpha\\.net/ORDO/Orphanet_[0-9]+)$</t>
+          <t>^(http://snomed\.info/id/[0-9]{6,18}|http://id\.who\.int/icd/entity/[0-9]+|http://www\.orpha\.net/ORDO/Orphanet_[0-9]+)$</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -2767,7 +2767,7 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -3237,7 +3237,7 @@
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -3423,7 +3423,7 @@
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -3661,7 +3661,7 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#IdentifierShape</t>
+          <t>http://data.health-ri.nl/core/p2/IdentifierShape</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3833,7 +3833,11 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/ProvenanceStatementShape</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -3847,12 +3851,12 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:DetailsViewer</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>dash:URIEditor</t>
+          <t>dash:BlankNodeEditor</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3897,7 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AgentShape</t>
+          <t>http://data.health-ri.nl/core/p2/AgentShape</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -4009,7 +4013,7 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#AttributionShape</t>
+          <t>http://data.health-ri.nl/core/p2/AttributionShape</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -4067,7 +4071,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#RelationshipShape</t>
+          <t>http://data.health-ri.nl/core/p2/RelationshipShape</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -4125,7 +4129,7 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#QualityCertificateShape</t>
+          <t>http://data.health-ri.nl/core/p2/QualityCertificateShape</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -4253,7 +4257,7 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#PeriodOfTimeShape</t>
+          <t>http://data.health-ri.nl/core/p2/PeriodOfTimeShape</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -4445,7 +4449,7 @@
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -4487,7 +4491,7 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#PeriodOfTimeShape</t>
+          <t>http://data.health-ri.nl/core/p2/PeriodOfTimeShape</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4631,7 +4635,7 @@
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -4751,7 +4755,7 @@
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -4793,7 +4797,7 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#TableGroupShape</t>
+          <t>http://data.health-ri.nl/core/p2/TableGroupShape</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4969,7 +4973,11 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/ActivityShape</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -4983,12 +4991,12 @@
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:DetailsViewer</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>dash:URIEditor</t>
+          <t>dash:BlankNodeEditor</t>
         </is>
       </c>
     </row>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:02</t>
+          <t>2026-10-26 13:15:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -2737,7 +2737,8 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Relates a dataset to a SNOMED CT, ICD-10, or ORPHAcode concept representing a disease, disorder, or other clinical condition that the dataset concerns as a whole.</t>
+          <t xml:space="preserve">	
+Relates a dataset to a SNOMED CT, ICD-10, ICD-11, or ORPHAcode concept representing a disease, disorder, or other clinical condition that the dataset concerns as a whole.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2756,7 +2757,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>^(http://snomed\.info/id/[0-9]{6,18}|http://id\.who\.int/icd/entity/[0-9]+|http://www\.orpha\.net/ORDO/Orphanet_[0-9]+)$</t>
+          <t>^(http://snomed[.]info/id/[0-9]+|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -4793,13 +4794,13 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>sh:IRI</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>http://data.health-ri.nl/core/p2/TableGroupShape</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -4813,12 +4814,12 @@
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>dash:DetailsViewer</t>
+          <t>dash:URIViewer</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>dash:BlankNodeEditor</t>
+          <t>dash:URIEditor</t>
         </is>
       </c>
     </row>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:49</t>
+          <t>2026-10-26 16:19:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:38</t>
+          <t>2026-10-27 15:44:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>^(http://snomed[.]info/id/[0-9]+|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
+          <t>^(http://snomed[.]info/id/[0-9]+|^http://id[.]who[.]int/icd/entity/[0-9]+$|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:12</t>
+          <t>2026-10-28 09:50:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -2757,7 +2757,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>^(http://snomed[.]info/id/[0-9]+|^http://id[.]who[.]int/icd/entity/[0-9]+$|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
+          <t>^(http://snomed[.]info/id/[0-9]+|http://id[.]who[.]int/icd/entity/[0-9]+|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-dataset.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:41</t>
+          <t>2026-10-28 11:04:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
